--- a/price_list.xlsx
+++ b/price_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erhan\Documents\Github\cargo_wings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E97821-62C5-4BC7-91DE-4A70D63AFC62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4ECAF1-D053-4B6A-94AD-066FD3306B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F1553EBD-527B-4C48-BFD8-1B6C18F70DD7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>DJI Tello</t>
   </si>
@@ -44,21 +44,9 @@
     <t>Raspberry Pi Zero W2</t>
   </si>
   <si>
-    <t>Orange Pi 5B</t>
-  </si>
-  <si>
-    <t>GSM Module SIM7600E</t>
-  </si>
-  <si>
     <t>DW1000-DEV Module</t>
   </si>
   <si>
-    <t>Camera Module</t>
-  </si>
-  <si>
-    <t>Orange Pi compatible touch display</t>
-  </si>
-  <si>
     <t>Bileşenler</t>
   </si>
   <si>
@@ -69,6 +57,21 @@
   </si>
   <si>
     <t>Toplam ($)</t>
+  </si>
+  <si>
+    <t>Raspberry Pi Zero Camera Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PCB </t>
+  </si>
+  <si>
+    <t>ESP32-DEV Module</t>
+  </si>
+  <si>
+    <t>PCB Power Bileşenleri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kargo </t>
   </si>
 </sst>
 </file>
@@ -127,9 +130,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -167,7 +170,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -273,7 +276,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -415,7 +418,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -423,7 +426,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AC1FFE-E02D-304D-A0BB-0415EB6CAB7A}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -433,16 +436,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -471,7 +474,7 @@
         <v>20</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D8" si="0">(B3*C3)</f>
+        <f t="shared" ref="D3" si="0">(B3*C3)</f>
         <v>100</v>
       </c>
     </row>
@@ -480,84 +483,99 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>150</v>
+        <v>35</v>
       </c>
       <c r="D4">
-        <f t="shared" si="0"/>
-        <v>300</v>
+        <f>(B4*C4)</f>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
-        <v>150</v>
+        <f>(B5*C5)</f>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
-        <v>350</v>
+        <f>(B6*C6)</f>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>5</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="D7">
-        <f t="shared" si="0"/>
-        <v>200</v>
+        <f>(B7*C7)</f>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <f t="shared" si="0"/>
-        <v>60</v>
+        <f>(B8*C8)</f>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>100</v>
+      </c>
       <c r="D9">
-        <f>SUM(D2:D8)</f>
-        <v>1910</v>
+        <f>(B9*C9)</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <f>SUM(D2:D9)</f>
+        <v>1655</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>